--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-ai-training-data.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-ai-training-data.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$31</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="147">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -402,6 +402,27 @@
   </si>
   <si>
     <t>http://example.org/fhir/eu-ai-transparency/ValueSet/ehds-data-category-vs</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose</t>
+  </si>
+  <si>
+    <t>ehdsSecondaryUsePurpose</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose.value[x]</t>
+  </si>
+  <si>
+    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/ehds-secondary-use-purpose-vs</t>
   </si>
   <si>
     <t>Extension.extension:ehdsPermit</t>
@@ -765,12 +786,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.48046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.89453125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.9921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.85546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.26953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -793,7 +814,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2708,7 +2729,7 @@
         <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>111</v>
@@ -2741,13 +2762,11 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
@@ -2801,7 +2820,7 @@
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>95</v>
@@ -3227,7 +3246,7 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>111</v>
@@ -3260,11 +3279,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -3300,26 +3321,28 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -3328,24 +3351,22 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>18</v>
@@ -3387,30 +3408,30 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>107</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3421,7 +3442,7 @@
         <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -3433,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3490,26 +3511,543 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI26" t="s" s="2">
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AJ29" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AK29" t="s" s="2">
         <v>107</v>
       </c>
     </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK26">
+  <autoFilter ref="A1:AK31">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -3519,7 +4057,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI25">
+  <conditionalFormatting sqref="A2:AI30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
